--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_406_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_406_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>17</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>7</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,7 +1335,7 @@
         <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>43:50</t>
+          <t>23:51</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>13.4%</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>33:05</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>14.7%</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>60:00</t>
+          <t>30:00</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>06:56</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AN21" t="n">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
@@ -2318,13 +2318,13 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>7</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>40:20</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -2431,22 +2431,22 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>19.6%</t>
         </is>
       </c>
     </row>
@@ -2511,10 +2511,10 @@
         <v>17</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>36:06</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>11.0%</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>36:17</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AN24" t="n">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>49.1%</t>
         </is>
       </c>
     </row>
@@ -2906,13 +2906,13 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>2</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>33:53</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AN25" t="n">
@@ -3019,17 +3019,17 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AN26" t="n">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AN27" t="n">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -3491,7 +3491,7 @@
         <v>21</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>57:23</t>
+          <t>27:20</t>
         </is>
       </c>
       <c r="AN28" t="n">
@@ -3607,22 +3607,22 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>27.6%</t>
         </is>
       </c>
     </row>
@@ -3827,16 +3827,16 @@
         <v>113</v>
       </c>
       <c r="T30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>38</v>
@@ -4292,16 +4292,16 @@
         <v>30</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>3</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>41:00</t>
+          <t>30:59</t>
         </is>
       </c>
       <c r="AN35" t="n">
@@ -4408,22 +4408,22 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>7.0%</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>57:07</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AN37" t="n">
@@ -4800,22 +4800,22 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>10.1%</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>31:35</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AN38" t="n">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>65:05</t>
+          <t>25:05</t>
         </is>
       </c>
       <c r="AN39" t="n">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>10.6%</t>
         </is>
       </c>
     </row>
@@ -5468,16 +5468,16 @@
         <v>24</v>
       </c>
       <c r="T41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>7</v>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>53:10</t>
+          <t>33:09</t>
         </is>
       </c>
       <c r="AN41" t="n">
@@ -5584,22 +5584,22 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>28.0%</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
         <v>7</v>
       </c>
       <c r="T42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>35:18</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AN42" t="n">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>10.6%</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>54:47</t>
+          <t>24:46</t>
         </is>
       </c>
       <c r="AN44" t="n">
@@ -6172,17 +6172,17 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="AN45" t="n">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.6%</t>
         </is>
       </c>
     </row>
@@ -6448,16 +6448,16 @@
         <v>12</v>
       </c>
       <c r="T46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>4</v>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>55:41</t>
+          <t>25:38</t>
         </is>
       </c>
       <c r="AN46" t="n">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>7.6%</t>
         </is>
       </c>
     </row>
@@ -6784,16 +6784,16 @@
         <v>91</v>
       </c>
       <c r="T48" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
         <v>25</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_406_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_406_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
         <v>17</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
         <v>7</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,7 +1335,7 @@
         <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -2318,13 +2318,13 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X22" t="n">
         <v>7</v>
@@ -2511,10 +2511,10 @@
         <v>17</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2906,13 +2906,13 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X25" t="n">
         <v>2</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3491,16 +3491,16 @@
         <v>21</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X28" t="n">
         <v>8</v>
@@ -3827,16 +3827,16 @@
         <v>113</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X30" t="n">
         <v>38</v>
@@ -4292,16 +4292,16 @@
         <v>30</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
         <v>3</v>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -5468,16 +5468,16 @@
         <v>24</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X41" t="n">
         <v>7</v>
@@ -5664,7 +5664,7 @@
         <v>7</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -6448,16 +6448,16 @@
         <v>12</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X46" t="n">
         <v>4</v>
@@ -6784,16 +6784,16 @@
         <v>91</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X48" t="n">
         <v>25</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_406_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_406_EL.xlsx
@@ -674,10 +674,10 @@
         <v>17</v>
       </c>
       <c r="N2" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="O2" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="P2" t="n">
         <v>4</v>
@@ -692,20 +692,20 @@
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>88.37</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -2131,14 +2131,14 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA21" t="n">
@@ -2327,10 +2327,10 @@
         <v>5</v>
       </c>
       <c r="X22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -2523,14 +2523,14 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2915,14 +2915,14 @@
         <v>2</v>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3307,14 +3307,14 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3503,10 +3503,10 @@
         <v>2</v>
       </c>
       <c r="X28" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y28" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -3536,25 +3536,25 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -3839,14 +3839,14 @@
         <v>9</v>
       </c>
       <c r="X30" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="Y30" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>88.4%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3872,25 +3872,25 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4304,14 +4304,14 @@
         <v>1</v>
       </c>
       <c r="X35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y35" t="n">
         <v>3</v>
       </c>
-      <c r="Y35" t="n">
-        <v>4</v>
-      </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -4892,10 +4892,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -5480,10 +5480,10 @@
         <v>2</v>
       </c>
       <c r="X41" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y41" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -5676,14 +5676,14 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -6068,14 +6068,14 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA44" t="n">
@@ -6796,14 +6796,14 @@
         <v>4</v>
       </c>
       <c r="X48" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="Y48" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="AA48" t="n">
